--- a/Phase - 7 Automation Testing/Assessment-2/automationExcersice/src/test/resources/dataset.xlsx
+++ b/Phase - 7 Automation Testing/Assessment-2/automationExcersice/src/test/resources/dataset.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXPLEO SMARTCLIFF\Phase - 7 Automation Testing\Assessment-2\automationExcersice\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0936F2DE-B93F-4FD3-B648-9E6CB4040740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C393C1EF-9AAE-4621-9057-03EED746854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SignUp" sheetId="1" r:id="rId1"/>
     <sheet name="Login" sheetId="2" r:id="rId2"/>
     <sheet name="InvalidLogin" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="ValidSearchKeys" sheetId="4" r:id="rId4"/>
+    <sheet name="InvalidSearchKeys" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>password</t>
   </si>
@@ -42,9 +43,6 @@
     <t>Invalid Search Keys</t>
   </si>
   <si>
-    <t>kiot</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
@@ -64,6 +62,12 @@
   </si>
   <si>
     <t>2k22cse169@kiot.ac.in</t>
+  </si>
+  <si>
+    <t>Valid Search Keys</t>
+  </si>
+  <si>
+    <t>Shirt</t>
   </si>
 </sst>
 </file>
@@ -400,35 +404,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -451,35 +455,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -501,35 +505,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -548,12 +552,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADF6F1B-200D-4862-83B0-8C7561FD671A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
